--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487058_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487058_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5511</v>
+        <v>2.2755</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5376</v>
+        <v>1.5565</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0135</v>
+        <v>0.719</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0064</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9617</v>
+        <v>0.6861</v>
       </c>
       <c r="T2" t="n">
-        <v>0.427</v>
+        <v>0.4459</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5347</v>
+        <v>0.2402</v>
       </c>
       <c r="V2" t="n">
         <v>4.9119</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3668</v>
+        <v>1.8496</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0382</v>
+        <v>1.6814</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6714</v>
+        <v>0.1682</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8053</v>
+        <v>1.5286</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1883</v>
+        <v>0.7618</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6169</v>
+        <v>0.7669</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2758</v>
+        <v>2.3823</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7399</v>
+        <v>1.0557</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.4641</v>
+        <v>1.3267</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0811</v>
+        <v>-0.8537</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9283</v>
+        <v>-0.2939</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1528</v>
+        <v>-0.5598</v>
       </c>
       <c r="P3" t="n">
         <v>1.3511</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3161</v>
+        <v>1.3511</v>
       </c>
       <c r="S3" t="n">
-        <v>1.821</v>
+        <v>-0.4161</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9857</v>
+        <v>-0.3728</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1646</v>
+        <v>-0.0433</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7418</v>
+        <v>-0.3281</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7418</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>J. SAEZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1546</v>
+        <v>1.1643</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2809</v>
+        <v>1.0219</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1263</v>
+        <v>0.1424</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5286</v>
+        <v>1.3276</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7618</v>
+        <v>1.1662</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7669</v>
+        <v>0.1614</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3823</v>
+        <v>2.2553</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0557</v>
+        <v>2.2146</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3267</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8537</v>
+        <v>-0.9277</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2939</v>
+        <v>-1.0484</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5598</v>
+        <v>0.1207</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1111</v>
+        <v>0.1153</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7733</v>
+        <v>-0.5542</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3378</v>
+        <v>0.6696</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>-0.8576</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3281</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>-1.1435</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SAEZ PEREZ</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9988</v>
+        <v>1.1539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8028</v>
+        <v>1.7012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.196</v>
+        <v>-0.5473</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3276</v>
+        <v>2.17</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1662</v>
+        <v>0.1365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1614</v>
+        <v>2.0335</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2553</v>
+        <v>3.9257</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2146</v>
+        <v>2.0128</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>1.9129</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9277</v>
+        <v>-1.7557</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0484</v>
+        <v>-1.8763</v>
       </c>
       <c r="O5" t="n">
         <v>0.1207</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0502</v>
+        <v>0.4049</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7733</v>
+        <v>-0.2945</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7231</v>
+        <v>0.6993</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8576</v>
+        <v>-1.228</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1435</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9486</v>
+        <v>1.0382</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2818</v>
+        <v>2.7364</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3331</v>
+        <v>-1.6982</v>
       </c>
       <c r="G6" t="n">
-        <v>2.17</v>
+        <v>-0.8053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1365</v>
+        <v>-0.1883</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0335</v>
+        <v>-0.6169</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9257</v>
+        <v>0.2758</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0128</v>
+        <v>0.7399</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9129</v>
+        <v>-0.4641</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7557</v>
+        <v>-1.0811</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8763</v>
+        <v>-0.9283</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1207</v>
+        <v>-0.1528</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1996</v>
+        <v>0.4925</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7139</v>
+        <v>0.6838</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9135</v>
+        <v>-0.1914</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.7418</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.228</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.741</v>
+        <v>0.6935</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8276</v>
+        <v>0.6806</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0867</v>
+        <v>0.0129</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.5262</v>
+        <v>-1.3308</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6404</v>
+        <v>-1.5329</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1142</v>
+        <v>0.2021</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8112</v>
+        <v>0.8313</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9576</v>
+        <v>-0.4711</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1464</v>
+        <v>1.3024</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7149</v>
+        <v>-2.1621</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6828</v>
+        <v>-1.0618</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0321</v>
+        <v>-1.1003</v>
       </c>
       <c r="P7" t="n">
-        <v>0.772</v>
+        <v>2.5091</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.386</v>
       </c>
       <c r="R7" t="n">
-        <v>1.158</v>
+        <v>2.8951</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2671</v>
+        <v>0.1292</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5111</v>
+        <v>-0.0505</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2439</v>
+        <v>0.1798</v>
       </c>
       <c r="V7" t="n">
-        <v>1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6761</v>
+        <v>0.1744</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.954</v>
+        <v>-2.536</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6301</v>
+        <v>2.7104</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3964</v>
@@ -1078,13 +1078,13 @@
         <v>3.0881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5863</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1455</v>
+        <v>-0.4366</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4409</v>
+        <v>0.5212</v>
       </c>
       <c r="V8" t="n">
         <v>0.3281</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5934</v>
+        <v>0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5805</v>
+        <v>1.3269</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0129</v>
+        <v>-1.167</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3308</v>
+        <v>-2.5262</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5329</v>
+        <v>-2.6404</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2021</v>
+        <v>0.1142</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8313</v>
+        <v>-0.8112</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4711</v>
+        <v>-0.9576</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3024</v>
+        <v>0.1464</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1621</v>
+        <v>-1.7149</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0618</v>
+        <v>-1.6828</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1003</v>
+        <v>-0.0321</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5091</v>
+        <v>0.772</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.386</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8951</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0291</v>
+        <v>0.6861</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1507</v>
+        <v>1.0104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1798</v>
+        <v>-0.3242</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1759</v>
+        <v>0.0779</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1718</v>
+        <v>0.0285</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0041</v>
+        <v>0.0494</v>
       </c>
       <c r="G10" t="n">
         <v>0.0743</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0357</v>
+        <v>0.2895</v>
       </c>
       <c r="T10" t="n">
-        <v>0.074</v>
+        <v>0.2743</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0383</v>
+        <v>0.0152</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>R. NUÑEZ HERRERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5668</v>
+        <v>-2.0222</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7196</v>
+        <v>0.1774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8472</v>
+        <v>-2.1996</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3751</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4376</v>
+        <v>-1.4201</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9375</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0275</v>
+        <v>1.3745</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.1292</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5048</v>
+        <v>1.2453</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3476</v>
+        <v>-0.8945</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9149</v>
+        <v>-1.5493</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4327</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3511</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3774</v>
+        <v>-0.004</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0873</v>
+        <v>-0.1246</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4647</v>
+        <v>0.1206</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5717</v>
+        <v>-2.4982</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5717</v>
+        <v>0.8576</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.3558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. NUÑEZ HERRERO</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7222</v>
+        <v>-2.1861</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4423</v>
+        <v>-1.4191</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2799</v>
+        <v>-0.7669</v>
       </c>
       <c r="G12" t="n">
-        <v>0.48</v>
+        <v>-2.3751</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4201</v>
+        <v>-1.4376</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>-0.9375</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3745</v>
+        <v>-1.0275</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1292</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2453</v>
+        <v>-0.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8945</v>
+        <v>-1.3476</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5493</v>
+        <v>-0.9149</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.4327</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-0.386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9301</v>
+        <v>-1.3511</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9301</v>
+        <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7039</v>
+        <v>0.0033</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7442</v>
+        <v>0.3877</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0403</v>
+        <v>-0.3844</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4982</v>
+        <v>0.5717</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8576</v>
+        <v>0.5717</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8001</v>
+        <v>-4.0188</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6916</v>
+        <v>-1.9906</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1086</v>
+        <v>-2.0283</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7492</v>
@@ -1468,13 +1468,13 @@
         <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4019</v>
+        <v>-0.6207</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8037</v>
+        <v>-0.1028</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5982</v>
+        <v>-0.5179</v>
       </c>
       <c r="V13" t="n">
         <v>-0.614</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2346000000000004</v>
+        <v>0.3601999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>4.370099999999999</v>
+        <v>4.965100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.604799999999999</v>
+        <v>-4.605</v>
       </c>
       <c r="G14" t="n">
         <v>-7.6089</v>
@@ -1546,16 +1546,16 @@
         <v>21.2308</v>
       </c>
       <c r="S14" t="n">
-        <v>1.256</v>
+        <v>1.8507</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2715000000000002</v>
+        <v>0.8660999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9848</v>
+        <v>0.9847000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3280000000000002</v>
+        <v>0.3280000000000003</v>
       </c>
       <c r="W14" t="n">
         <v>10.7983</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.2475</v>
+        <v>8.533300000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.6508</v>
+        <v>7.7495</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5967</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>4.7284</v>
@@ -1624,13 +1624,13 @@
         <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9558</v>
+        <v>0.2416</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1991</v>
+        <v>0.2978</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2433</v>
+        <v>-0.0562</v>
       </c>
       <c r="V15" t="n">
         <v>2.2123</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5425</v>
+        <v>7.0104</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7011</v>
+        <v>4.5008</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8414</v>
+        <v>2.5097</v>
       </c>
       <c r="G16" t="n">
         <v>3.2643</v>
@@ -1702,13 +1702,13 @@
         <v>2.8951</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4746</v>
+        <v>-0.0066</v>
       </c>
       <c r="T16" t="n">
-        <v>0.041</v>
+        <v>-0.1593</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5155999999999999</v>
+        <v>0.1526</v>
       </c>
       <c r="V16" t="n">
         <v>0.8576</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4983</v>
+        <v>1.0422</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.007</v>
+        <v>-0.0213</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5054</v>
+        <v>1.0635</v>
       </c>
       <c r="G17" t="n">
-        <v>9.0509</v>
+        <v>-3.0213</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3345</v>
+        <v>0.4681</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7165</v>
+        <v>-3.4894</v>
       </c>
       <c r="J17" t="n">
-        <v>9.0709</v>
+        <v>-1.4864</v>
       </c>
       <c r="K17" t="n">
-        <v>6.0028</v>
+        <v>1.6973</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0682</v>
+        <v>-3.1838</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02</v>
+        <v>-1.5348</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6683</v>
+        <v>-1.2292</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6483</v>
+        <v>-0.3056</v>
       </c>
       <c r="P17" t="n">
-        <v>-10.2294</v>
+        <v>2.1231</v>
       </c>
       <c r="Q17" t="n">
-        <v>-12.5455</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3161</v>
+        <v>3.0881</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5334</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1898</v>
+        <v>-0.3116</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7231</v>
+        <v>-0.204</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1435</v>
+        <v>2.4559</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6573</v>
+        <v>2.7418</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3281</v>
+        <v>0.7096</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3217</v>
+        <v>-1.2059</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0063</v>
+        <v>1.9155</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.0213</v>
+        <v>9.0509</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4681</v>
+        <v>5.3345</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.4894</v>
+        <v>3.7165</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4864</v>
+        <v>9.0709</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6973</v>
+        <v>6.0028</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.1838</v>
+        <v>3.0682</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5348</v>
+        <v>-0.02</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2292</v>
+        <v>-0.6683</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3056</v>
+        <v>0.6483</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1231</v>
+        <v>-10.2294</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>-12.5455</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0881</v>
+        <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8858</v>
+        <v>0.7446</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.612</v>
+        <v>-0.3886</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2738</v>
+        <v>1.1332</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4559</v>
+        <v>1.1435</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7418</v>
+        <v>2.6573</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2859</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1438</v>
+        <v>-0.7766</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0865</v>
+        <v>2.1866</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2303</v>
+        <v>-2.9633</v>
       </c>
       <c r="G20" t="n">
         <v>0.6005</v>
@@ -2014,13 +2014,13 @@
         <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2076</v>
+        <v>0.1596</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2247</v>
+        <v>-0.1246</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0172</v>
+        <v>0.2842</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5717</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7864</v>
+        <v>-1.1651</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2355</v>
+        <v>0.0649</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5509</v>
+        <v>-1.23</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0448</v>
@@ -2092,13 +2092,13 @@
         <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8996</v>
+        <v>-0.2783</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2234</v>
+        <v>0.077</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6762</v>
+        <v>-0.3553</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6075</v>
+        <v>-2.5808</v>
       </c>
       <c r="E22" t="n">
         <v>-1.7904</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8171</v>
+        <v>-0.7903</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6749</v>
@@ -2170,13 +2170,13 @@
         <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1606</v>
+        <v>-0.1338</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7903</v>
+        <v>-4.0956</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8379</v>
+        <v>-3.4373</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9525</v>
+        <v>-0.6583</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8786</v>
@@ -2248,13 +2248,13 @@
         <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5909</v>
+        <v>0.1038</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3873</v>
+        <v>0.0132</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2036</v>
+        <v>0.0905</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9311</v>
+        <v>-5.9735</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5815</v>
+        <v>-3.3826</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3496</v>
+        <v>-2.5909</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1422</v>
@@ -2326,13 +2326,13 @@
         <v>1.158</v>
       </c>
       <c r="S24" t="n">
-        <v>1.667</v>
+        <v>0.6246</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6504</v>
+        <v>-0.1507</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0165</v>
+        <v>0.7753</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6839</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2345999999999995</v>
+        <v>2.237399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>4.604900000000001</v>
+        <v>4.604799999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.370200000000001</v>
+        <v>-2.367299999999999</v>
       </c>
       <c r="G25" t="n">
         <v>7.6088</v>
@@ -2404,13 +2404,13 @@
         <v>15.4405</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2559</v>
+        <v>0.7469000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9847</v>
+        <v>-0.9847999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2713999999999999</v>
+        <v>1.7314</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3280999999999996</v>
